--- a/content/docs/monograph/gemini/gemini 참고자료.xlsx
+++ b/content/docs/monograph/gemini/gemini 참고자료.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\soometro\content\docs\monograph\gemini\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE879378-92CB-49D7-BF24-50BD8F4445F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6B26BF-A1EC-489E-B83F-61F48140D414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15945" activeTab="1" xr2:uid="{72A92B6D-868C-45EB-BFF4-EF9DDAEFC8B2}"/>
+    <workbookView xWindow="11903" yWindow="698" windowWidth="14760" windowHeight="14467" activeTab="1" xr2:uid="{72A92B6D-868C-45EB-BFF4-EF9DDAEFC8B2}"/>
   </bookViews>
   <sheets>
     <sheet name="가로" sheetId="2" r:id="rId1"/>
